--- a/docs/项目文档索引.xlsx
+++ b/docs/项目文档索引.xlsx
@@ -37,7 +37,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +86,12 @@
         <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5A6BD"/>
+        <bgColor rgb="00D5A6BD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -113,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -137,6 +143,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -504,14 +513,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="75" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
   </cols>
@@ -554,10 +563,8 @@
       </c>
     </row>
     <row r="2" ht="38" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -591,10 +598,8 @@
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A3" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -628,10 +633,8 @@
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A4" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -665,10 +668,8 @@
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A5" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -702,10 +703,8 @@
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A6" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -739,10 +738,8 @@
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A7" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -776,10 +773,8 @@
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A8" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -813,10 +808,8 @@
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A9" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -850,10 +843,8 @@
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A10" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -887,10 +878,8 @@
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A11" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -924,10 +913,8 @@
       </c>
     </row>
     <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A12" s="2" t="n">
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -961,10 +948,8 @@
       </c>
     </row>
     <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A13" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
@@ -998,10 +983,8 @@
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="A14" s="2" t="n">
+        <v>13</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
@@ -1035,10 +1018,8 @@
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="A15" s="2" t="n">
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
@@ -1072,10 +1053,8 @@
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="A16" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
@@ -1109,10 +1088,8 @@
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="A17" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
@@ -1146,10 +1123,8 @@
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="A18" s="2" t="n">
+        <v>17</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
@@ -1183,10 +1158,8 @@
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A19" s="2" t="n">
+        <v>18</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
@@ -1220,10 +1193,8 @@
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="A20" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
@@ -1257,10 +1228,8 @@
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="A21" s="2" t="n">
+        <v>20</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
@@ -1293,6 +1262,192 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="38" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>create_config_xlsx.py</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>工具脚本</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>create_config_xlsx.py</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\create_config_xlsx.py</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- 创建 config.xlsx 配置文件 A列项目名 = 变量归属：</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="38" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>主程序</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\main.py</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- main.py - 京东商智数据导出工具（重构版 v2.0） 本文件集中存放：</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="38" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>main_old_backup.py</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>main_old_backup.py</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\main_old_backup.py</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- main.py FYA箱包旗舰店 - 京东商智数据导出 - 主程序入口</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="38" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>update_doc_index.py</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>工具脚本</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>update_doc_index.py</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\update_doc_index.py</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>项目文档索引自动更新工具：扫描项目.md/.py，追加新文件到索引xlsx</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>手动入库 2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="38" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>create_doc_index_xlsx.py</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>工具脚本</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>create_doc_index_xlsx.py</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\create_doc_index_xlsx.py</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- create_doc_index_xlsx.py ============================================================</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="38" customHeight="1"/>
+    <row r="28" ht="38" customHeight="1"/>
+    <row r="29" ht="38" customHeight="1"/>
+    <row r="30" ht="38" customHeight="1"/>
+    <row r="31" ht="38" customHeight="1"/>
+    <row r="32" ht="38" customHeight="1"/>
+    <row r="33" ht="38" customHeight="1"/>
+    <row r="34" ht="38" customHeight="1"/>
+    <row r="35" ht="38" customHeight="1"/>
+    <row r="36" ht="38" customHeight="1"/>
+    <row r="37" ht="38" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1304,10 +1459,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1332,22 +1487,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>全局规则</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Trae Agent 全局底线，禁止写业务细节；每次启动自动加载。</t>
+          <t>Trae Skill 业务分组（按需加载，不被全局自动注入）。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>架构规范</t>
+          <t>业务知识</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -1355,67 +1510,97 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>项目目录结构、命名规则、代码组织方式。</t>
+          <t>踩坑日志、API 实现逻辑文档等业务沉淀。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>业务知识</t>
+          <t>主程序</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>踩坑日志、API 实现逻辑文档等业务沉淀。</t>
+          <t>项目主入口（如 main.py）。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>全局规则</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Trae Skill 业务分组（按需加载，不被全局自动注入）。</t>
+          <t>Trae Agent 全局底线，禁止写业务细节；每次启动自动加载。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>文件夹说明</t>
+          <t>工具脚本</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>每个目录的 FOLDER_NAME.md，描述目录用途。</t>
+          <t>项目辅助工具（create_*.py 等）。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>文件夹说明</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>每个目录的 FOLDER_NAME.md，描述目录用途。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>架构规范</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>项目目录结构、命名规则、代码组织方式。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>脚本</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Python 脚本（如 Playwright 抓包脚本）。</t>
+      <c r="B9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Python 业务脚本（如 Playwright 抓包脚本）。</t>
         </is>
       </c>
     </row>

--- a/docs/项目文档索引.xlsx
+++ b/docs/项目文档索引.xlsx
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>

--- a/docs/项目文档索引.xlsx
+++ b/docs/项目文档索引.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="�� 文档总索引" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="�� 分类汇总" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="�� 文档总索引" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="�� 分类汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -92,6 +92,12 @@
         <bgColor rgb="00D5A6BD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -119,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -146,6 +152,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -513,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1437,10 +1446,146 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="38" customHeight="1"/>
-    <row r="28" ht="38" customHeight="1"/>
-    <row r="29" ht="38" customHeight="1"/>
-    <row r="30" ht="38" customHeight="1"/>
+    <row r="27" ht="38" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>JZT_KUAICHE_SKILL.md</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>docs/JZT_KUAICHE_SKILL.md</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\docs\JZT_KUAICHE_SKILL.md</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t># 京准通快车自定义报表｜业务沉淀 Skill &gt; 本文件按需加载，覆盖京准通 jzt.jd.com 快车自定义报表业务。 &gt; 上线时间：2026-08-07（阶段3 骨架 → 阶段10 完整三步流程）</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="38" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>jzt_quanzhan_effect_unittest.py</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>tests/jzt_quanzhan_effect_unittest.py</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\tests\jzt_quanzhan_effect_unittest.py</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- """项目10：京准通全站营销单品推广效果报表导出（mock 单测）。 ⚠️ 不发真请求，使用 unittest.mock 拦截 requests.Session.post / requests.get。</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="38" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>jzt_quanzhan_all_store_unittest.py</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>tests/jzt_quanzhan_all_store_unittest.py</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\tests\jzt_quanzhan_all_store_unittest.py</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- """项目11：京准通全站营销全店计划报表导出（mock 单测）。 ⚠️ 不发真请求，使用 unittest.mock 拦截 requests.Session.post / requests.get。</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="38" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>jzt_quanzhan_effect_all_store_unittest.py</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>tests/jzt_quanzhan_effect_all_store_unittest.py</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\tests\jzt_quanzhan_effect_all_store_unittest.py</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- """项目12：京准通全站营销全店推广效果报表导出（mock 单测）。 ⚠️ 不发真请求，使用 unittest.mock 拦截 requests.Session.post / requests.get。</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-10</t>
+        </is>
+      </c>
+    </row>
     <row r="31" ht="38" customHeight="1"/>
     <row r="32" ht="38" customHeight="1"/>
     <row r="33" ht="38" customHeight="1"/>
@@ -1459,7 +1604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1577,28 +1722,43 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>架构规范</t>
+          <t>文档</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>项目目录结构、命名规则、代码组织方式。</t>
+          <t>其他通用 .md 文档。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>脚本</t>
+          <t>架构规范</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>项目目录结构、命名规则、代码组织方式。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Python 业务脚本（如 Playwright 抓包脚本）。</t>
         </is>

--- a/docs/项目文档索引.xlsx
+++ b/docs/项目文档索引.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1586,13 +1586,321 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="38" customHeight="1"/>
-    <row r="32" ht="38" customHeight="1"/>
-    <row r="33" ht="38" customHeight="1"/>
-    <row r="34" ht="38" customHeight="1"/>
-    <row r="35" ht="38" customHeight="1"/>
-    <row r="36" ht="38" customHeight="1"/>
-    <row r="37" ht="38" customHeight="1"/>
+    <row r="31" ht="38" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>config_manager.py</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>config_manager.py</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\config_manager.py</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- """多店铺配置管理器（2026-08-12 启动） 职责：</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="38" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>一键全部跑指南.md</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>docs/一键全部跑指南.md</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\docs\一键全部跑指南.md</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t># 一键全部跑指南（2026-08-12） &gt; 适用版本：main.py ≥ 217cda0（项目16 售后明细 + 项目17 多店铺管理 已入库） &gt; 目的：列出 `BUSINESS_REGISTRY` 全部 19 个业务 key 的可用命令模板，复制即可跑。</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="38" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>多店铺管理_RPA自动化指南.md</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>docs/多店铺管理_RPA自动化指南.md</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\docs\多店铺管理_RPA自动化指南.md</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t># 多店铺管理 &amp; RPA 自动抓取指南（项目17，2026-08-12） ## 1. 目标 让让可以通过 **影刀 RPA** 自动抓取 Cookie + h5st，按店铺 ID 写入 `config/{店铺ID}/` 目录，Python 端自动读取最新值并用于接口调用。</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="38" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>维护手册.md</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>docs/维护手册.md</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\docs\维护手册.md</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t># 京东数据导出工具 - 维护手册（2026-08-11） &gt; 本文档是仓库维护的**唯一权威来源**，所有过期项、重抓流程、影刀配置都汇总在此。 &gt; 配套工具：`maintain.py`（自动检测脚本）</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="38" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>maintain.py</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>maintain.py</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\maintain.py</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- maintain.py - 自动检测过期项工具（项目15，2026-08-11） ============================================================</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="38" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>auth_loader.py</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>auth_loader.py</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\auth_loader.py</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- """多店铺鉴权加载器（2026-08-13 上线） 职责（用户决策 2026-08-13）：</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="38" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>auth_writer.py</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>auth_writer.py</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\auth_writer.py</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- """影刀 RPA 写鉴权 JSON 的辅助工具（项目19，2026-08-13） 职责：</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="38" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>RPA集成指南.md</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>docs/RPA集成指南.md</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\docs\RPA集成指南.md</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t># 影刀 RPA 集成指南（项目19，2026-08-13） &gt; 适用版本：main.py ≥ b2ab6f3（项目18 AuthLoader 已入库） &gt; 目的：让影刀 RPA 全自动跑京东数据导出，包含多店铺切换、鉴权抓取、Python 业务调用</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="38" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>module1.py</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>module1.py</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\module1.py</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- """影刀 RPA 调用的 Python 入口（项目19，2026-08-13） 职责：</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1726,7 +2034,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -1756,7 +2064,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>

--- a/docs/项目文档索引.xlsx
+++ b/docs/项目文档索引.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="�� 文档总索引" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="�� 分类汇总" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="�� 文档总索引" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="�� 分类汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1898,6 +1898,601 @@
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>自动入库 @ 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="38" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>DB_USAGE.md</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>DB_USAGE.md</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\DB_USAGE.md</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t># 数据库集成使用说明（项目21，2026-08-14） &gt; 适用版本：main.py ≥ 5645769 &gt; 目的：将 20 个京东数据报表（Excel）持久化到本地 SQLite 数据库，支持每日自动滚动更新与缺失补录。</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="38" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>biz_config_loader.py</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>biz_config_loader.py</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\biz_config_loader.py</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- """biz_config_loader.py ============================================================</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="38" customHeight="1">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>daily_update.py</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>daily_update.py</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\daily_update.py</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- daily_update.py ============================================================</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="38" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>db_utils.py</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>db_utils.py</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\db_utils.py</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- db_utils.py ============================================================</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="38" customHeight="1">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22_Excel总表实现说明.md</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>docs/2026-08-22_Excel总表实现说明.md</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\docs\2026-08-22_Excel总表实现说明.md</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t># Excel 总表双输出实现说明（项目24） &gt; **生效时间**：2026-08-22 &gt; **作者**：Trae Agent</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="38" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22_H高危审计修复报告.md</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>docs/2026-08-22_H高危审计修复报告.md</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\docs\2026-08-22_H高危审计修复报告.md</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t># 2026-08-22 H 高危审计修复报告 &gt; 任务背景：审计发现 9 条高危必须修复（H-01~H-09） &gt; 修复策略：禁止硬编码兜底，所有业务常量从 runtime_config 统一加载</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="38" customHeight="1">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>config参数维护指南.md</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>docs/config参数维护指南.md</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\docs\config参数维护指南.md</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t># config.xlsx 可调整参数维护指南（2026-08-21 新增） &gt; 本文档是**轻量日常维护**手册，与 `docs/维护手册.md`（Cookie / h5st 重抓）互补。 &gt;</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="38" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>三店拆分方案.md</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>docs/三店拆分方案.md</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\docs\三店拆分方案.md</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t># 三店拆分方案（2026-08-21 设计稿，待用户确认后实施） ## 一、目标 - 当前 main.py 10,119 行单文件 → 拆为 4 个文件</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="38" customHeight="1">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>项目文件清单.md</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>docs/项目文件清单.md</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\docs\项目文件清单.md</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t># FYA箱包旗舰店 · 项目文件清单 &gt; **生成日期**：2026-08-21 &gt; **扫描范围**：`d:\CODE\trae\traespace\FYA箱包旗舰店`</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="38" customHeight="1">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>excel_master.py</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>excel_master.py</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\excel_master.py</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- """excel_master.py ============================================================</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="38" customHeight="1">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>fill_missing.py</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>fill_missing.py</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\fill_missing.py</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- fill_missing.py ============================================================</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="38" customHeight="1">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>imap_config_loader.py</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>imap_config_loader.py</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\imap_config_loader.py</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- """imap_config_loader.py ============================================================</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="38" customHeight="1">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>FOLDER_NAME.md</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>文件夹说明</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>output/FYA箱包旗舰店/FOLDER_NAME.md</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\output\FYA箱包旗舰店\FOLDER_NAME.md</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t># 📂 文件夹命名说明：output ## 基本信息 | 项 | 内容 |</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="38" customHeight="1">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>refresh_reports.py</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>refresh_reports.py</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\refresh_reports.py</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- """refresh_reports.py ============================================================</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="38" customHeight="1">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>rpa_run.py</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>rpa_run.py</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\rpa_run.py</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- """多店铺数据导出手动触发入口（项目22，2026-08-17） 用户决策 2026-08-17：</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="38" customHeight="1">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>runtime_config.py</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>runtime_config.py</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\runtime_config.py</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- """runtime_config.py ============================================================</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="38" customHeight="1">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>excel_master_unittest.py</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>tests/excel_master_unittest.py</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>D:\CODE\trae\traespace\FYA箱包旗舰店\tests\excel_master_unittest.py</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t># -*- coding: utf-8 -*- """excel_master 自测脚本（2026-08-22 项目24） 4 个核心场景（用户 spec 第九节）：</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>自动入库 @ 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2614,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -2034,7 +2629,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -2064,7 +2659,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
